--- a/output/details/2026-05-16/preprocessed_data.xlsx
+++ b/output/details/2026-05-16/preprocessed_data.xlsx
@@ -15231,25 +15231,25 @@
         <v>46158</v>
       </c>
       <c r="B2" t="n">
-        <v>-0.110401618432494</v>
+        <v>-0.1121330625594054</v>
       </c>
       <c r="C2" t="n">
-        <v>0.1715611100126267</v>
+        <v>-0.1385639554889703</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1713200470903873</v>
+        <v>-0.1382909360820084</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.1284845127798729</v>
+        <v>0.001850689802161836</v>
       </c>
       <c r="F2" t="n">
-        <v>0.001701814333465031</v>
+        <v>0.001700464681410607</v>
       </c>
       <c r="G2" t="n">
-        <v>1.870374489856398</v>
+        <v>2.446041520487725</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.449466173289971</v>
+        <v>-0.264015420764417</v>
       </c>
       <c r="I2" t="n">
         <v>1</v>
